--- a/Sprint/src/test/resources/Data/TrainSearchData.xlsx
+++ b/Sprint/src/test/resources/Data/TrainSearchData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ritam\Programming\Capgemini\java\Sprint\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33416BDE-8C48-4C7C-B59D-827A3E2B2107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CEB7A7-5D0F-4511-8CC3-9356A5618DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="2" xr2:uid="{607278AB-24F0-4CFC-B742-8598C0E0EB38}"/>
   </bookViews>
@@ -36,19 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
   <si>
     <t>fromInput</t>
   </si>
@@ -92,9 +80,6 @@
     <t>Chennai Central</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>date</t>
   </si>
   <si>
@@ -120,6 +105,36 @@
   </si>
   <si>
     <t>e7x98hdKX</t>
+  </si>
+  <si>
+    <t>data_id</t>
+  </si>
+  <si>
+    <t>VS_01</t>
+  </si>
+  <si>
+    <t>VS_02</t>
+  </si>
+  <si>
+    <t>VS_03</t>
+  </si>
+  <si>
+    <t>DS_01</t>
+  </si>
+  <si>
+    <t>DS_02</t>
+  </si>
+  <si>
+    <t>DS_03</t>
+  </si>
+  <si>
+    <t>IS_01</t>
+  </si>
+  <si>
+    <t>IS_02</t>
+  </si>
+  <si>
+    <t>IS_03</t>
   </si>
 </sst>
 </file>
@@ -485,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81966295-2170-4891-865C-7CBE3A8BEBF1}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.08984375" customWidth="1"/>
@@ -494,75 +509,79 @@
     <col min="4" max="4" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -571,7 +590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8531EC-6B26-4991-835F-F9BDFFE50DC1}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.26953125" customWidth="1"/>
@@ -580,90 +599,92 @@
     <col min="4" max="4" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -672,68 +693,75 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903629EF-9427-479F-BBDC-32748497F8FE}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.08984375" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
     <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sprint/src/test/resources/Data/TrainSearchData.xlsx
+++ b/Sprint/src/test/resources/Data/TrainSearchData.xlsx
@@ -1,23 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ritam\Programming\Capgemini\java\Sprint\src\test\resources\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CEB7A7-5D0F-4511-8CC3-9356A5618DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DEC7606E-2493-42A0-A25B-3C49354D022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="2" xr2:uid="{607278AB-24F0-4CFC-B742-8598C0E0EB38}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{607278AB-24F0-4CFC-B742-8598C0E0EB38}"/>
   </bookViews>
   <sheets>
     <sheet name="ValidSearch" sheetId="1" r:id="rId1"/>
     <sheet name="DateSearch" sheetId="2" r:id="rId2"/>
     <sheet name="InvalidSearch" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:O23"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>fromInput</t>
   </si>
@@ -81,12 +77,6 @@
   </si>
   <si>
     <t>date</t>
-  </si>
-  <si>
-    <t>today</t>
-  </si>
-  <si>
-    <t>tomorrow</t>
   </si>
   <si>
     <t>Pat</t>
@@ -511,7 +501,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -528,7 +518,7 @@
     </row>
     <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -545,7 +535,7 @@
     </row>
     <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -562,7 +552,7 @@
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -601,7 +591,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -621,7 +611,7 @@
     </row>
     <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -635,13 +625,13 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
@@ -655,28 +645,28 @@
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
         <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -704,7 +694,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -713,12 +703,12 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -727,12 +717,12 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
@@ -741,12 +731,12 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -755,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
